--- a/results/climate_change_breakdown/2025/propanol production, DAC carbon dioxide, wind hydrogen, fossil ethylene_GLO.xlsx
+++ b/results/climate_change_breakdown/2025/propanol production, DAC carbon dioxide, wind hydrogen, fossil ethylene_GLO.xlsx
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.650284729086457</v>
+        <v>1.446787350332405</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.2499034041554336</v>
+        <v>0.0480128523582264</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.001227715689559049</v>
+        <v>5.247355369227052E-05</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.0005820794841199426</v>
+        <v>0.000150491774581528</v>
       </c>
       <c r="E8">
         <v>1</v>
